--- a/assignment/mod 10 API testing/api_complete_test_report.xlsx
+++ b/assignment/mod 10 API testing/api_complete_test_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sneha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c7dd620d9e945120/Desktop/tops/assignment/mod 10 API testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8216EBD1-BDAA-43BF-A2C5-BF4082F31CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{8216EBD1-BDAA-43BF-A2C5-BF4082F31CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50FEF30B-D811-432B-8687-E2B296D08DB4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Functional Testing" sheetId="1" r:id="rId1"/>
@@ -1362,188 +1362,188 @@
   </cellStyleXfs>
   <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1827,381 +1827,381 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
     </row>
     <row r="3" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="49" t="s">
         <v>320</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="5">
         <v>200</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="10" t="s">
+      <c r="K5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="5">
         <v>200</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="10" t="s">
+      <c r="K6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="52" t="s">
         <v>321</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="13">
         <v>200</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="16" t="s">
+      <c r="K7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="13">
         <v>201</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="16" t="s">
+      <c r="K8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="10">
         <v>400</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="16" t="s">
+      <c r="K9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="5">
         <v>200</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="10" t="s">
+      <c r="K10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="52" t="s">
         <v>318</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="10">
         <v>404</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="16" t="s">
+      <c r="K11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="12">
         <v>400</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="10" t="s">
+      <c r="K12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2245,529 +2245,529 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
     </row>
     <row r="3" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="23" t="s">
+      <c r="L4" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="12">
         <v>400</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="10" t="s">
+      <c r="K5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="10">
         <v>429</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="16" t="s">
+      <c r="K6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="51" t="s">
         <v>316</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="12">
+        <v>404</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="10">
+        <v>403</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="12">
+        <v>401</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="10">
+        <v>401</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="12">
         <v>400</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="25" t="s">
+      <c r="H11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="10">
+        <v>400</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="5">
+        <v>200</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="22" t="s">
+      <c r="K13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G14" s="13">
+        <v>200</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="5">
+        <v>200</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D16" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="18">
-        <v>403</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="20">
-        <v>401</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J9" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>319</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="18">
-        <v>401</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="G11" s="20">
-        <v>400</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="60" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="G12" s="18">
-        <v>400</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="E16" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G16" s="13">
         <v>200</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="J13" s="25" t="s">
+      <c r="H16" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J16" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="60" t="s">
-        <v>322</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="G14" s="21">
-        <v>200</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="J14" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="61" t="s">
-        <v>320</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="G15" s="13">
-        <v>200</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="G16" s="21">
-        <v>200</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="J16" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="K16" s="28" t="s">
+      <c r="K16" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="L16" s="8" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2807,611 +2807,611 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
     </row>
     <row r="3" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="22">
         <v>10</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="22">
         <v>500</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="5">
         <v>312</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="5">
         <v>145</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="12">
         <v>890</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="22">
         <v>16</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="23">
         <v>0</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="12" t="s">
+      <c r="M5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="24">
         <v>50</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="24">
         <v>2000</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="13">
         <v>487</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="13">
         <v>180</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="10">
         <v>1450</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="24">
         <v>40.200000000000003</v>
       </c>
-      <c r="K6" s="33">
+      <c r="K6" s="25">
         <v>0.4</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="L6" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="17" t="s">
+      <c r="M6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="22">
         <v>200</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="22">
         <v>1000</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="12">
         <v>1240</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="5">
         <v>210</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="12">
         <v>4500</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="22">
         <v>14.8</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="26">
         <v>2.1</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="4" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="24">
         <v>10</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="24">
         <v>1000</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="13">
         <v>218</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="13">
         <v>98</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="10">
         <v>540</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="24">
         <v>45.6</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="27">
         <v>0</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L8" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="M8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="17" t="s">
+      <c r="M8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="22">
         <v>100</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="22">
         <v>5000</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="5">
         <v>385</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="5">
         <v>102</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="12">
         <v>980</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="22">
         <v>128.19999999999999</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="28">
         <v>0.2</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="M9" s="28" t="s">
+      <c r="M9" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="N9" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="24">
         <v>5</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="24">
         <v>200</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="13">
         <v>195</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="13">
         <v>90</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="13">
         <v>420</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="24">
         <v>10.3</v>
       </c>
-      <c r="K10" s="35">
+      <c r="K10" s="27">
         <v>0</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L10" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="M10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="17" t="s">
+      <c r="M10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="22">
         <v>10</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="22">
         <v>500</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="5">
         <v>274</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="5">
         <v>120</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="12">
         <v>620</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="22">
         <v>18.2</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="23">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="M11" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="12" t="s">
+      <c r="M11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="24">
         <v>50</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="24">
         <v>2000</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="13">
         <v>441</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="13">
         <v>135</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="10">
         <v>1100</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="24">
         <v>45.3</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="25">
         <v>0.6</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L12" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="M12" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="17" t="s">
+      <c r="M12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="22">
         <v>20</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="22">
         <v>2000</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="5">
         <v>156</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="5">
         <v>60</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="5">
         <v>380</v>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="22">
         <v>128.69999999999999</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="23">
         <v>0</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="M13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="12" t="s">
+      <c r="M13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="24">
         <v>200</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="24">
         <v>10000</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="13">
         <v>234</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="13">
         <v>68</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="10">
         <v>720</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="24">
         <v>420.1</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="25">
         <v>0.1</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L14" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="M14" s="28" t="s">
+      <c r="M14" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N14" s="9" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="22">
         <v>50</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="22">
         <v>90000</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="5">
         <v>188</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="5">
         <v>62</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="12">
         <v>510</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="22">
         <v>50</v>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="28">
         <v>0.05</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="M15" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="12" t="s">
+      <c r="M15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="4" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="52" t="s">
         <v>318</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="24">
         <v>10</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="24">
         <v>300</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="13">
         <v>198</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="13">
         <v>88</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="13">
         <v>460</v>
       </c>
-      <c r="J16" s="32">
+      <c r="J16" s="24">
         <v>15.2</v>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="27">
         <v>0</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="L16" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="M16" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" s="17" t="s">
+      <c r="M16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="9" t="s">
         <v>194</v>
       </c>
     </row>
@@ -3451,770 +3451,770 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="55" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="29">
         <v>200</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J5" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="10" t="s">
+      <c r="J5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="32">
         <v>400</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="16" t="s">
+      <c r="J6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="34">
         <v>409</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="I7" s="39" t="s">
+      <c r="I7" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J7" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="10" t="s">
+      <c r="J7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="32">
         <v>400</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="16" t="s">
+      <c r="J8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="29">
         <v>200</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="J9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="52" t="s">
         <v>324</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="32">
         <v>401</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="16" t="s">
+      <c r="J10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="34">
         <v>400</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J11" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="10" t="s">
+      <c r="J11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="52" t="s">
         <v>324</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="32">
         <v>400</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="H12" s="40" t="s">
+      <c r="H12" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="I12" s="41" t="s">
+      <c r="I12" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J12" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="16" t="s">
+      <c r="J12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="29">
         <v>200</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J13" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="10" t="s">
+      <c r="J13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="52" t="s">
         <v>321</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="32">
         <v>401</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="H14" s="40" t="s">
+      <c r="H14" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="I14" s="41" t="s">
+      <c r="I14" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J14" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="16" t="s">
+      <c r="J14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="29">
         <v>201</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="10" t="s">
+      <c r="J15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="32">
         <v>401</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="I16" s="41" t="s">
+      <c r="I16" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J16" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="16" t="s">
+      <c r="J16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="34">
         <v>401</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="I17" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J17" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="10" t="s">
+      <c r="J17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="32">
         <v>409</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="I18" s="41" t="s">
+      <c r="I18" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J18" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="16" t="s">
+      <c r="J18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="49" t="s">
         <v>317</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="29">
         <v>200</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J19" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="10" t="s">
+      <c r="J19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="52" t="s">
         <v>317</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="32">
         <v>401</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="I20" s="41" t="s">
+      <c r="I20" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J20" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="16" t="s">
+      <c r="J20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="29">
         <v>200</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H21" s="37" t="s">
+      <c r="H21" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="I21" s="39" t="s">
+      <c r="I21" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J21" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="10" t="s">
+      <c r="J21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="52" t="s">
         <v>318</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="32">
         <v>404</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J22" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="16" t="s">
+      <c r="J22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="F23" s="42">
+      <c r="F23" s="34">
         <v>401</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H23" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="I23" s="39" t="s">
+      <c r="I23" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="J23" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="10" t="s">
+      <c r="J23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="52" t="s">
         <v>318</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="32">
         <v>400</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="I24" s="41" t="s">
+      <c r="I24" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="J24" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="16" t="s">
+      <c r="J24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4262,370 +4262,370 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="54" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="55" t="s">
         <v>280</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="43" t="s">
+      <c r="C4" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="35" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="44">
+      <c r="B5" s="36">
         <v>17</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="37">
         <v>17</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="38">
         <v>0</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="39">
         <v>0</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="36">
         <v>12</v>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="37">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="43" t="s">
+      <c r="C8" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="H8" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="43" t="s">
+      <c r="H8" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="35" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="44">
+      <c r="B9" s="36">
         <v>12</v>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="37">
         <v>8</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="39">
         <v>2</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="38">
         <v>2</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="36">
         <v>20</v>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="37">
         <v>20</v>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="40" t="s">
         <v>288</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="40">
         <v>61</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="41">
         <v>56</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="42">
         <v>3</v>
       </c>
-      <c r="H12" s="51" t="s">
+      <c r="H12" s="43" t="s">
         <v>291</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="60" t="s">
         <v>292</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="1" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="22">
         <v>8</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="22">
         <v>8</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="22">
         <v>0</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="22">
         <v>0</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="24" t="s">
         <v>301</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="24">
         <v>12</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="24">
         <v>11</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="24">
         <v>1</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="24">
         <v>0</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="22">
         <v>12</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="22">
         <v>8</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="22">
         <v>2</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="22">
         <v>2</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="20" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="24" t="s">
         <v>304</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="24">
         <v>20</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="24">
         <v>20</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="24">
         <v>0</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="24">
         <v>0</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="61" t="s">
         <v>305</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
     </row>
     <row r="23" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="44" t="s">
         <v>306</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
     </row>
     <row r="24" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="45" t="s">
         <v>308</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="58" t="s">
         <v>309</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
     </row>
     <row r="25" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="59" t="s">
         <v>311</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
     </row>
     <row r="26" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="58" t="s">
         <v>313</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
     </row>
     <row r="27" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="59" t="s">
         <v>315</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="9">
